--- a/AVANCE DE ESCRITURA JUNIO/TABLAS Y FIGURAS BONITAS REV1.xlsx
+++ b/AVANCE DE ESCRITURA JUNIO/TABLAS Y FIGURAS BONITAS REV1.xlsx
@@ -1,26 +1,536 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Angeal\Desktop\GNLPDA\AVANCE DE ESCRITURA JUNIO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB35DB5-6F20-491B-BF0F-B7EE07D9FE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja4" sheetId="4" r:id="rId4"/>
+    <sheet name="Hoja5" sheetId="5" r:id="rId5"/>
+    <sheet name="Hoja6" sheetId="6" r:id="rId6"/>
+    <sheet name="Hoja7" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hoja7!$B$1:$B$89</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="146">
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Variables</t>
+  </si>
+  <si>
+    <t>penguins</t>
+  </si>
+  <si>
+    <t>pimadiabetes</t>
+  </si>
+  <si>
+    <t>wines</t>
+  </si>
+  <si>
+    <t>Cebolla3D</t>
+  </si>
+  <si>
+    <t>Cebolla10D</t>
+  </si>
+  <si>
+    <t>Cebolla20D</t>
+  </si>
+  <si>
+    <t>Breast Cancer (WDBC)</t>
+  </si>
+  <si>
+    <t>Ionosphere</t>
+  </si>
+  <si>
+    <t>Clases</t>
+  </si>
+  <si>
+    <t>Muestras</t>
+  </si>
+  <si>
+    <t>Linealmente separable</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Complicado</t>
+  </si>
+  <si>
+    <t>No lineal</t>
+  </si>
+  <si>
+    <t>Indicadores 2015</t>
+  </si>
+  <si>
+    <t>Indicadores 2020</t>
+  </si>
+  <si>
+    <t>No se sabe</t>
+  </si>
+  <si>
+    <t>Parámetro</t>
+  </si>
+  <si>
+    <t>Valor final</t>
+  </si>
+  <si>
+    <t>Selección</t>
+  </si>
+  <si>
+    <t>Torneo binario</t>
+  </si>
+  <si>
+    <t>Cruza</t>
+  </si>
+  <si>
+    <t>Un punto</t>
+  </si>
+  <si>
+    <t>Representación</t>
+  </si>
+  <si>
+    <t>Binaria</t>
+  </si>
+  <si>
+    <t>Elitismo</t>
+  </si>
+  <si>
+    <t>Número de generaciones</t>
+  </si>
+  <si>
+    <t>Tamaño de población</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilidad de cruza </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilidad de mutación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penalización por complejidad </t>
+  </si>
+  <si>
+    <t>2 mejores 
+individuos</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Rango de búsqueda</t>
+  </si>
+  <si>
+    <t>Real</t>
+  </si>
+  <si>
+    <t>Entero</t>
+  </si>
+  <si>
+    <t>[0.05,0.2]</t>
+  </si>
+  <si>
+    <t>ngen</t>
+  </si>
+  <si>
+    <t>[20,100]</t>
+  </si>
+  <si>
+    <t>pobsize</t>
+  </si>
+  <si>
+    <t>prob cruza</t>
+  </si>
+  <si>
+    <t>[0.4,0.95]</t>
+  </si>
+  <si>
+    <t>Penalizador</t>
+  </si>
+  <si>
+    <t>[0.01,0.2]</t>
+  </si>
+  <si>
+    <t>prob muta</t>
+  </si>
+  <si>
+    <t>Caso</t>
+  </si>
+  <si>
+    <t>Atributos</t>
+  </si>
+  <si>
+    <t>Muestras 
+por clase</t>
+  </si>
+  <si>
+    <t>Atributos 
+expandido</t>
+  </si>
+  <si>
+    <t>Propósito en la comparación</t>
+  </si>
+  <si>
+    <t>Línea base lineal y proyectiva; implementación usada internamente por GNLPDA</t>
+  </si>
+  <si>
+    <t>Clasificador discriminante con fronteras cuadráticas</t>
+  </si>
+  <si>
+    <t>Alternativa kernel de Fisher para separación no lineal</t>
+  </si>
+  <si>
+    <t>Comparación frente a una transformación polinomial implícita de segundo grado</t>
+  </si>
+  <si>
+    <t>Comparación frente a una transformación polinomial implícita de mayor orden</t>
+  </si>
+  <si>
+    <t>Clasificador kernel no lineal ampliamente utilizado</t>
+  </si>
+  <si>
+    <t>LDA MASS</t>
+  </si>
+  <si>
+    <t>QDA</t>
+  </si>
+  <si>
+    <t>KFDA</t>
+  </si>
+  <si>
+    <t>SVM</t>
+  </si>
+  <si>
+    <t>Gauss</t>
+  </si>
+  <si>
+    <t>Pol (3)</t>
+  </si>
+  <si>
+    <t>Pol (2)</t>
+  </si>
+  <si>
+    <t>Clásico</t>
+  </si>
+  <si>
+    <t>Método</t>
+  </si>
+  <si>
+    <t>Variante</t>
+  </si>
+  <si>
+    <t>LDA de la paqueteria MASS</t>
+  </si>
+  <si>
+    <t>Asaduzzaman, A., Uddin, M. R., &amp; Sibai, F. N. (2024). Dimensionality reduction by machine learning for cost-effective data analysis.</t>
+  </si>
+  <si>
+    <t>Barradas-Palmeros, J.-A., Mezura-Montes, E., Rivera-López, R., &amp; Acosta-Mesa, H.-G. (2024). Computational cost reduction in wrapper approaches for feature selection: A case of study using permutational-based differential evolution. 2024 IEEE Congress on Evolutionary Computation (CEC), 1–8.</t>
+  </si>
+  <si>
+    <t>Bharadiya, J. P. (2023). A tutorial on principal component analysis for dimensionality reduction in machine learning. International Journal of Innovative Science and Research Technology, 8(5), 2028–2032.</t>
+  </si>
+  <si>
+    <t>Bishop, C. M., &amp; Nasrabadi, N. M. (2006). Pattern recognition and machine learning (Vol. 4). Springer.</t>
+  </si>
+  <si>
+    <t>Danubianu, M., Pentiuc, S. G., &amp; Danubianu, D. M. (2012). Data dimensionality reduction for data mining: A combined filter-wrapper framework. International Journal Of Computers Communications &amp; Control, 7(5), 824–831.</t>
+  </si>
+  <si>
+    <t>Feng, S., &amp; Wang, H. (2021). Comparison of PCA and LDA dimensionality reduction algorithms based on wine dataset. 2021 33rd Chinese Control and Decision Conference (CCDC), 2791–2796.</t>
+  </si>
+  <si>
+    <t>Fisher, R. A. (1936). The use of multiple measurements in taxonomic problems. Annals of Eugenics, 7(2), 179–188.</t>
+  </si>
+  <si>
+    <t>Gao, H., &amp; Davis, J. W. (2006). Why direct LDA is not equivalent to LDA. Pattern Recognition, 39(5), 1002–1006.</t>
+  </si>
+  <si>
+    <t>Härdle, W., &amp; Simar, L. (2007). Applied multivariate statistical analysis. Springer.</t>
+  </si>
+  <si>
+    <t>Huang, R., Liu, Q., Lu, H., &amp; Ma, S. (2002). Solving the small sample size problem of LDA. 2002 International Conference on Pattern Recognition, 3, 29–32.</t>
+  </si>
+  <si>
+    <t>Kanade, V. (2016). Basis expansion, regularization, validation.</t>
+  </si>
+  <si>
+    <t>Kohavi, R., &amp; John, G. H. (1997). Wrappers for feature subset selection. Artificial Intelligence, 97(1-2), 273–324.</t>
+  </si>
+  <si>
+    <t>Li, T., Zhu, S., &amp; Ogihara, M. (2006). Using discriminant analysis for multi-class classification: An experimental investigation. Knowledge and Information Systems, 10(4), 453–472.</t>
+  </si>
+  <si>
+    <t>Marsaglia, G. (1972). Choosing a point from the surface of a sphere. The Annals of Mathematical Statistics, 43(2), 645–646.</t>
+  </si>
+  <si>
+    <t>Martinez, A. M., &amp; Kak, A. C. (2001). Pca versus lda. IEEE Transactions on Pattern Analysis and Machine Intelligence, 23(2), 228–233.</t>
+  </si>
+  <si>
+    <t>McLachlan, G. J. (2005). Discriminant analysis and statistical pattern recognition. John Wiley &amp; Sons.</t>
+  </si>
+  <si>
+    <t>Medina, V. D. G., Mesa, H. G. A., &amp; Lobato, A. L. L. (2025). Genetic projective discriminant analysis.</t>
+  </si>
+  <si>
+    <t>Niu, G., &amp; Ma, Z. (2021). Local quasi-linear embedding based on kronecker product expansion of vectors. Journal of Intelligent &amp; Fuzzy Systems, 41(1), 2195–2205.</t>
+  </si>
+  <si>
+    <t>Palo, H. K., Sahoo, S., &amp; Subudhi, A. K. (2021). Dimensionality reduction techniques: Principles, benefits, and limitations. Data Analytics in Bioinformatics: A Machine Learning Perspective, 77–107.</t>
+  </si>
+  <si>
+    <t>Sharma, A., &amp; Paliwal, K. K. (2015). Linear discriminant analysis for the small sample size problem: An overview. International Journal of Machine Learning and Cybernetics, 6(3), 443–454.</t>
+  </si>
+  <si>
+    <t>Silalahi, D. D., Reaño, C. E., Lansigan, F. P., Panopio, R. G., &amp; Bantayan, N. C. (n.d.). Linear discriminant analysis vs. Genetic algorithm neural network with principal component analysis for hyperdimensional data analysis: A study on ripeness grading of oil palm (elaeis guineensis jacq.) fresh fruit. Philippine Statistician, 65(2).</t>
+  </si>
+  <si>
+    <t>Sorzano, C. O. S., Vargas, J., &amp; Montano, A. P. (2014). A survey of dimensionality reduction techniques. arXiv Preprint arXiv:1403.2877.</t>
+  </si>
+  <si>
+    <t>Ultsch, A. (2004). Strategies for an artificial life system to cluster high dimensional data. Abstracting and Synthesizing the Principles of Living Systems, GWAL-6, 128–137.</t>
+  </si>
+  <si>
+    <t>Wani, A. A. (2025). Comprehensive review of dimensionality reduction algorithms: Challenges, limitations, and innovative solutions. PeerJ Computer Science, 11, e3025.</t>
+  </si>
+  <si>
+    <t>Agatra, D. F. N., Marutho, D., &amp; Xiong, X. (2025). Evaluating PCA and LDA to improve machine learning classification of consumer behavior in health informatics. Journal of Intelligent Computing and Health Informatics (JICHI). Vol, 6(1).</t>
+  </si>
+  <si>
+    <t>Al-Milli, N., Hudaib, A., &amp; Obeid, N. (2021). Population diversity control of genetic algorithm using a novel injection method for bankruptcy prediction problem. Mathematics, 9(8), 823.</t>
+  </si>
+  <si>
+    <t>Araveeporn, A., &amp; Banditvilai, S. (2023). A classification study in high-dimensional data of linear discriminant analysis and regularized discriminant analysis. WSEAS Trans. Math, 22, 315–323.</t>
+  </si>
+  <si>
+    <t>Bahlool, R., Hewahi, N., &amp; Harrath, Y. (2025). FastTree-guided genetic algorithm for credit scoring feature selection. Computers, 14(12), 566.</t>
+  </si>
+  <si>
+    <t>Barth, J., Katumullage, D., Yang, C., &amp; Cao, J. (2021). Classification of wines using principal component analysis. Journal of Wine Economics, 16(1), 56–67.</t>
+  </si>
+  <si>
+    <t>Belhumeur, P. N., Hespanha, J. P., &amp; Kriegman, D. J. (2002). Eigenfaces vs. Fisherfaces: Recognition using class specific linear projection. IEEE Transactions on Pattern Analysis and Machine Intelligence, 19(7), 711–720.</t>
+  </si>
+  <si>
+    <t>Briscik, M., Dillies, M.-A., &amp; Déjean, S. (2023). Improvement of variables interpretability in kernel PCA. BMC Bioinformatics, 24(1), 282.</t>
+  </si>
+  <si>
+    <r>
+      <t>Buhas, B. A., Muntean, L. A.-M., Ploussard, G., Feciche, B. O., Andras, I., Toma, V., Maghiar, T. A., Cri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ș</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Gill Sans MT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">an, N., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ș</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Gill Sans MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>tiufiuc, R.-I., &amp; Lucaciu, C. M. (2024). Renal cell carcinoma discrimination through attenuated total reflection fourier transform infrared spectroscopy of dried human urine and machine learning techniques. International Journal of Molecular Sciences, 25(18), 9830.</t>
+    </r>
+  </si>
+  <si>
+    <t>Chandrashekar, G., &amp; Sahin, F. (2014). A survey on feature selection methods. Computers &amp; Electrical Engineering, 40(1), 16–28.</t>
+  </si>
+  <si>
+    <t>Cortes, C., &amp; Vapnik, V. (1995). Support-vector networks. Machine Learning, 20(3), 273–297.</t>
+  </si>
+  <si>
+    <t>Cover, T. M. (1965). Geometrical and statistical properties of systems of linear inequalities with applications in pattern recognition. IEEE Transactions on Electronic Computers, (3), 326–334.</t>
+  </si>
+  <si>
+    <t>Demšar, J. (2006). Statistical comparisons of classifiers over multiple data sets. Journal of Machine Learning Research, 7(Jan), 1–30.</t>
+  </si>
+  <si>
+    <t>Du, K.-L., Jiang, B., Lu, J., Hua, J., &amp; Swamy, M. (2024). Exploring kernel machines and support vector machines: Principles, techniques, and future directions. Mathematics, 12(24), 3935.</t>
+  </si>
+  <si>
+    <t>Duda, R., Hart, P., Stork, D., &amp; Ionescu, A. (2000). Pattern classification. Wiley-Interscience Publication.</t>
+  </si>
+  <si>
+    <t>Friedman, J. H. (1989). Regularized discriminant analysis. Journal of the American Statistical Association, 84(405), 165–175.</t>
+  </si>
+  <si>
+    <t>Fukunaga, K. (2013). Introduction to statistical pattern recognition. Elsevier.</t>
+  </si>
+  <si>
+    <t>Goldberg, D. E. (1989). Genetic algorithms in search, optimization, and machine learning. Addison-Wesley.</t>
+  </si>
+  <si>
+    <t>Golub, G. H., &amp; Van Loan, C. F. (2013). Matrix computations. JHU press.</t>
+  </si>
+  <si>
+    <t>Guyon, I., &amp; Elisseeff, A. (2003). An introduction to variable and feature selection. Journal of Machine Learning Research, 3(Mar), 1157–1182.</t>
+  </si>
+  <si>
+    <t>Hastie, T., Tibshirani, R., Friedman, J., et al. (2009). The elements of statistical learning. Springer series in statistics New-York.</t>
+  </si>
+  <si>
+    <t>Horst, A. M., Hill, A. P., &amp; Gorman, K. B. (2022). Palmer archipelago penguins data in the palmerpenguins r package-an alternative to anderson’s irises. R Journal, 14(1).</t>
+  </si>
+  <si>
+    <t>Jain, A. K., Duin, R. P. W., &amp; Mao, J. (2000). Statistical pattern recognition: A review. IEEE Transactions on Pattern Analysis and Machine Intelligence, 22(1), 4–37.</t>
+  </si>
+  <si>
+    <t>Jalili, A., Saleki, Z., Luo, Y., Pan, F., Chen, A. X., &amp; Draayer, J. P. (2025). Performance of various kernel functions for mass prediction with support vector machine. The European Physical Journal A, 61(6), 143.</t>
+  </si>
+  <si>
+    <t>Kanade, V. (2016). Machine Learning – Michaelmas Term 2016: Lectures 4, 5: Basis Expansion, Regularization, Validation. Lecture notes, Department of Computer Science, University of Oxford. https://www.cs.ox.ac.uk/people/varun.kanade/teaching/ML-MT2016/lectures/lecture04.pdf</t>
+  </si>
+  <si>
+    <t>Kim, D., Park, S. H., &amp; Baek, J.-G. (2018). A KERNEL FISHER DISCRIMINANT ANALYSIS-BASED TREE ENSEMBLE CLASSIFIER: KFDA FOREST. International Journal of Industrial Engineering, 25(5).</t>
+  </si>
+  <si>
+    <t>Krzanowski, W. J., Jonathan, P., McCarthy, W., &amp; Thomas, M. R. (1995). Discriminant analysis with singular covariance matrices: Methods and applications to spectroscopic data. Journal of the Royal Statistical Society Series C: Applied Statistics, 44(1), 101–115.</t>
+  </si>
+  <si>
+    <t>Lara-Arellano, E., Takacs, A., Tovar-Arriaga, S., &amp; Rodrı́guez-Reséndiz, J. (2025). Feature generation with genetic algorithms for imagined speech electroencephalogram signal classification. Eng, 6(4), 75.</t>
+  </si>
+  <si>
+    <t>Li, Z., Nie, F., Wang, R., &amp; Li, X. (2024). A revised formation of trace ratio LDA for small sample size problem. IEEE Transactions on Neural Networks and Learning Systems.</t>
+  </si>
+  <si>
+    <t>Liu, J., Feng, M., Xiu, X., Liu, W., &amp; Zeng, X. (2024). Efficient and robust sparse linear discriminant analysis for data classification. IEEE Transactions on Emerging Topics in Computational Intelligence, 9(1), 617–629.</t>
+  </si>
+  <si>
+    <t>López-Ibáñez, M., Dubois-Lacoste, J., Cáceres, L. P., Birattari, M., &amp; Stützle, T. (2016). The irace package: Iterated racing for automatic algorithm configuration. Operations Research Perspectives, 3, 43–58.</t>
+  </si>
+  <si>
+    <t>Manhrawy, I. I., Fathi, H., Alsekait, D. M., Altawil, A., &amp; Kelany, A. K. (2026). Hybrid feature selection and classification model using high-dimensional data based on a metaheuristic algorithm for brain cancer diagnosis. Scientific Reports.</t>
+  </si>
+  <si>
+    <t>Martirosyan, V. (2026). Polynomial regression models for interpretable machine learning: Theory, optimization, and medical applications.</t>
+  </si>
+  <si>
+    <t>Medina, M. A., Davis, R. A., &amp; Samorodnitsky, G. (2025). Insights into kernel PCA with application to multivariate extremes. SIAM Journal on Mathematics of Data Science, 7(2), 777–801.</t>
+  </si>
+  <si>
+    <t>Mika, S., Ratsch, G., Weston, J., Scholkopf, B., &amp; Mullers, K.-R. (1999). Fisher discriminant analysis with kernels. Neural Networks for Signal Processing IX: Proceedings of the 1999 IEEE Signal Processing Society Workshop (Cat. No. 98th8468), 41–48.</t>
+  </si>
+  <si>
+    <t>Montgomery, D. C., Peck, E. A., &amp; Vining, G. G. (2021). Introduction to linear regression analysis. John Wiley &amp; Sons.</t>
+  </si>
+  <si>
+    <t>Mourik, F. van, Haeri, M. A., Bukhsh, F. A., &amp; Ahmed, F. (2024). IterSHAP: An XAI-based feature selection method for small high-dimensional datasets. Proceedings of the Future Technologies Conference, 526–545.</t>
+  </si>
+  <si>
+    <t>Pereira, D. G., Afonso, A., &amp; Medeiros, F. M. (2015). Overview of friedman’s test and post-hoc analysis. Communications in Statistics-Simulation and Computation, 44(10), 2636–2653.</t>
+  </si>
+  <si>
+    <t>Raudys, S. J., Jain, A. K., et al. (1991). Small sample size effects in statistical pattern recognition: Recommendations for practitioners. IEEE Transactions on Pattern Analysis and Machine Intelligence, 13(3), 252–264.</t>
+  </si>
+  <si>
+    <t>Remaki, L. (2026). RBF kernel parameter formula for data classification methods. arXiv Preprint arXiv:2604.01258.</t>
+  </si>
+  <si>
+    <t>Rudin, C. (2019). Stop explaining black box machine learning models for high stakes decisions and use interpretable models instead. Nature Machine Intelligence, 1(5), 206–215.</t>
+  </si>
+  <si>
+    <t>Salama, G. I., Abdelhalim, M., &amp; Zeid, M. (2012). Breast cancer diagnosis on three different datasets using multi-classifiers. Breast Cancer (WDBC), 32(569), 2.</t>
+  </si>
+  <si>
+    <t>Scholkopf, B., &amp; Smola, A. J. (2018). Learning with kernels: Support vector machines, regularization, optimization, and beyond. MIT press.</t>
+  </si>
+  <si>
+    <t>Shi, W., &amp; Wu, G. (2024). New algorithms for trace-ratio problem with application to high-dimension and large-sample data dimensionality reduction. Machine Learning, 113(7), 3889–3916.</t>
+  </si>
+  <si>
+    <t>Siedlecki, W., &amp; Sklansky, J. (1989). A note on genetic algorithms for large-scale feature selection. Pattern Recognition Letters, 10(5), 335–347.</t>
+  </si>
+  <si>
+    <t>Sigillito, V. (1989). Johns hopkins university ionosphere database. Johns Hopkins University, Baltimore, MD, USA.</t>
+  </si>
+  <si>
+    <t>Smith, J. W., Everhart, J. E., Dickson, W. C., Knowler, W. C., &amp; Johannes, R. S. (1988). Using the ADAP learning algorithm to forecast the onset of diabetes mellitus. Proceedings of the Annual Symposium on Computer Application in Medical Care, 261.</t>
+  </si>
+  <si>
+    <t>Tang, J., Alelyani, S., &amp; Liu, H. (2014). Feature selection for classification: A review. Data Classification: Algorithms and Applications, 37.</t>
+  </si>
+  <si>
+    <t>Venables, W. N., &amp; Ripley, B. D. (2013). Modern applied statistics with s. Springer Science &amp; Business Media.</t>
+  </si>
+  <si>
+    <t>Wang, Y., Fan, R., Cheng, L., Gong, B., &amp; Liu, J. (2026). An improved adaptive NSGA-II with multiple filtering for high-dimensional feature selection. Electronics, 15(1), 236.</t>
+  </si>
+  <si>
+    <t>Wang, Y., Gao, X., Ru, X., Sun, P., &amp; Wang, J. (2022). A hybrid feature selection algorithm and its application in bioinformatics. PeerJ Computer Science, 8, e933.</t>
+  </si>
+  <si>
+    <t>Yang, H., Lin, D., &amp; Li, Q. (2023). An efficient greedy search algorithm for high-dimensional linear discriminant analysis. Statistica Sinica, 33(SI), 1343.</t>
+  </si>
+  <si>
+    <t>Zhang, M., Treder, M., Marshall, D., &amp; Li, Y. (2024). Fast explanation of RBF-kernel SVM models using activation patterns. 2024 International Joint Conference on Neural Networks (IJCNN), 1–8.</t>
+  </si>
+  <si>
+    <t>Referencias</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +538,77 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +616,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -66,6 +676,82 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Imagen 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23141694-1699-FD7D-260E-B3B434D126FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="762000" y="11487150"/>
+          <a:ext cx="85725" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +1016,1281 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:F12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7">
+        <v>342</v>
+      </c>
+      <c r="D3" s="7">
+        <v>4</v>
+      </c>
+      <c r="E3" s="7">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="7">
+        <v>178</v>
+      </c>
+      <c r="D4" s="7">
+        <v>13</v>
+      </c>
+      <c r="E4" s="7">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7">
+        <v>569</v>
+      </c>
+      <c r="D5" s="7">
+        <v>30</v>
+      </c>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7">
+        <v>351</v>
+      </c>
+      <c r="D6" s="7">
+        <v>34</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="7">
+        <v>300</v>
+      </c>
+      <c r="D7" s="7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7">
+        <v>300</v>
+      </c>
+      <c r="D8" s="7">
+        <v>10</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7">
+        <v>300</v>
+      </c>
+      <c r="D9" s="7">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7">
+        <v>768</v>
+      </c>
+      <c r="D10" s="7">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2446</v>
+      </c>
+      <c r="D11" s="7">
+        <v>12</v>
+      </c>
+      <c r="E11" s="7">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2470</v>
+      </c>
+      <c r="D12" s="7">
+        <v>12</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B65E1C-9B7D-42D0-B69B-48D45C721FC3}">
+  <dimension ref="B4:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4">
+        <v>94</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="4">
+        <v>64</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="2:6" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC19336-4C98-4D8D-A333-F30F4D02FBC8}">
+  <dimension ref="B3:D8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B526D1F-3D59-49DA-AB47-5F128BD5F69B}">
+  <dimension ref="B3:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="2:6" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7">
+        <v>342</v>
+      </c>
+      <c r="D4" s="7">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="7">
+        <v>178</v>
+      </c>
+      <c r="D5" s="7">
+        <v>13</v>
+      </c>
+      <c r="E5" s="7">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="2:6" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="7">
+        <v>569</v>
+      </c>
+      <c r="D6" s="7">
+        <v>30</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="7">
+        <v>351</v>
+      </c>
+      <c r="D7" s="7">
+        <v>34</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7">
+        <v>300</v>
+      </c>
+      <c r="D8" s="7">
+        <v>3</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7">
+        <v>300</v>
+      </c>
+      <c r="D9" s="7">
+        <v>10</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7">
+        <v>300</v>
+      </c>
+      <c r="D10" s="7">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="2:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="7">
+        <v>768</v>
+      </c>
+      <c r="D11" s="7">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="2:6" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2446</v>
+      </c>
+      <c r="D12" s="7">
+        <v>12</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="2:6" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2470</v>
+      </c>
+      <c r="D13" s="7">
+        <v>12</v>
+      </c>
+      <c r="E13" s="7">
+        <v>5</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B219DB73-ED5A-4930-AD6C-4851D04CB31C}">
+  <dimension ref="B2:G9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4">
+        <v>150</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>150</v>
+      </c>
+      <c r="D4" s="4">
+        <v>10</v>
+      </c>
+      <c r="E4" s="4">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4">
+        <v>3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4">
+        <v>65</v>
+      </c>
+      <c r="F6" s="4">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4">
+        <v>135</v>
+      </c>
+      <c r="F7" s="4">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4">
+        <v>135</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4">
+        <v>17</v>
+      </c>
+      <c r="E9" s="4">
+        <v>170</v>
+      </c>
+      <c r="F9" s="4">
+        <v>3</v>
+      </c>
+      <c r="G9" s="4">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A1EE2D-3673-4362-8E7D-E550BB38B8BA}">
+  <dimension ref="F6:H12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="66.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="6:8" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="F6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="6:8" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="F7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="6:8" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="F8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="6:8" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="F9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="6:8" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="F10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="6:8" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="F11" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="6:8" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="F12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00647CBF-2CAB-4901-B4D7-9A6355A6F811}">
+  <dimension ref="B1:B79"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:B89" xr:uid="{00647CBF-2CAB-4901-B4D7-9A6355A6F811}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B89">
+      <sortCondition ref="B1:B89"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AVANCE DE ESCRITURA JUNIO/TABLAS Y FIGURAS BONITAS REV1.xlsx
+++ b/AVANCE DE ESCRITURA JUNIO/TABLAS Y FIGURAS BONITAS REV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Angeal\Desktop\GNLPDA\AVANCE DE ESCRITURA JUNIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB35DB5-6F20-491B-BF0F-B7EE07D9FE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3046366-DB32-4D9D-85F1-09CD7AE6B2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,12 @@
     <sheet name="Hoja5" sheetId="5" r:id="rId5"/>
     <sheet name="Hoja6" sheetId="6" r:id="rId6"/>
     <sheet name="Hoja7" sheetId="7" r:id="rId7"/>
+    <sheet name="Hoja8" sheetId="8" r:id="rId8"/>
+    <sheet name="Hoja9" sheetId="9" r:id="rId9"/>
+    <sheet name="Hoja10" sheetId="10" r:id="rId10"/>
+    <sheet name="Hoja11" sheetId="11" r:id="rId11"/>
+    <sheet name="Hoja12" sheetId="12" r:id="rId12"/>
+    <sheet name="Hoja13" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hoja7!$B$1:$B$89</definedName>
@@ -45,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="231">
   <si>
     <t>Dataset</t>
   </si>
@@ -525,12 +531,282 @@
   <si>
     <t>Referencias</t>
   </si>
+  <si>
+    <t>Autor y fecha</t>
+  </si>
+  <si>
+    <t>Yang et al. (2023); Araveeporn &amp; Banditvilai (2023)</t>
+  </si>
+  <si>
+    <t>Variantes Lineales (LDA Regularizado)</t>
+  </si>
+  <si>
+    <t>Agatra et al. (2025); Buhas et al. (2024)</t>
+  </si>
+  <si>
+    <t>Variantes Lineales (PCA-LDA)</t>
+  </si>
+  <si>
+    <t>Li et al. (2024); Shi &amp; Wu (2024)</t>
+  </si>
+  <si>
+    <t>Variantes Lineales (Trace-Ratio)</t>
+  </si>
+  <si>
+    <t>Medina et al. (2025); Briscik et al. (2023); Du et al. (2024)</t>
+  </si>
+  <si>
+    <t>Métodos Kernel (KPCA, KFDA)</t>
+  </si>
+  <si>
+    <t>Jalili et al. (2025); Remaki (2026)</t>
+  </si>
+  <si>
+    <t>Métodos Kernel (SVM)</t>
+  </si>
+  <si>
+    <t>Modelan fronteras altamente no lineales; exigen control estricto de parámetros para evitar sobreajuste.</t>
+  </si>
+  <si>
+    <t>Al-Milli et al. (2021); Wang et al. (2026)</t>
+  </si>
+  <si>
+    <t>Selección Evolutiva (Algoritmos Genéticos)</t>
+  </si>
+  <si>
+    <t>Wang et al. (2022); Manhrawy et al. (2026)</t>
+  </si>
+  <si>
+    <t>Métodos Híbridos</t>
+  </si>
+  <si>
+    <t>Medina et al. (2025)</t>
+  </si>
+  <si>
+    <t>Selección Evolutiva (GPDA)</t>
+  </si>
+  <si>
+    <t>Añaden regularización al modelo clásico para 
+estabilizar matrices en problemas de alta dimensionalidad.</t>
+  </si>
+  <si>
+    <t>Reducen la dimensionalidad en dos etapas 
+para eliminar redundancia antes de clasificar.</t>
+  </si>
+  <si>
+    <t>Optimizan directamente la relación de 
+dispersión interclase/intraclase para matrices singulares.</t>
+  </si>
+  <si>
+    <t>Emplean mapeos no lineales para
+ separar clases complejas, asumiendo pérdida de interpretabilidad.</t>
+  </si>
+  <si>
+    <t>Extraen subconjuntos de variables evadiendo óptimos
+ locales sin incurrir en costos computacionales prohibitivos.</t>
+  </si>
+  <si>
+    <t>Combinan filtrado estadístico inicial con 
+metaheurísticas para acelerar la selección de variables.</t>
+  </si>
+  <si>
+    <t>Maximizan la separabilidad evaluando proyecciones 
+directamente mediante el índice de silueta (sin invertir matrices).</t>
+  </si>
+  <si>
+    <t>Contibución</t>
+  </si>
+  <si>
+    <t>Apartado</t>
+  </si>
+  <si>
+    <t>Tabla 1: Estado del arte</t>
+  </si>
+  <si>
+    <t>X₁</t>
+  </si>
+  <si>
+    <t>X₂</t>
+  </si>
+  <si>
+    <t>X₁²</t>
+  </si>
+  <si>
+    <t>X₁X₂</t>
+  </si>
+  <si>
+    <t>X₂²</t>
+  </si>
+  <si>
+    <t>Componente</t>
+  </si>
+  <si>
+    <t>Configuración</t>
+  </si>
+  <si>
+    <t>Fit1 = Accuracy(cv5) – λ(n/N)
+Fit2 = Accuracy(cv5) – λ(n*/N*)</t>
+  </si>
+  <si>
+    <t>Selección de padres</t>
+  </si>
+  <si>
+    <t>Toreno binario</t>
+  </si>
+  <si>
+    <t>Oprador de cruza</t>
+  </si>
+  <si>
+    <t>Cruza de un solo punto</t>
+  </si>
+  <si>
+    <t>Operador de mutación</t>
+  </si>
+  <si>
+    <t>Mutación bit flip</t>
+  </si>
+  <si>
+    <t>Los mejores 2 de la generación pasan directo</t>
+  </si>
+  <si>
+    <t>Mecanismo de remplazo</t>
+  </si>
+  <si>
+    <t>Reemplazo generacional con elitismo</t>
+  </si>
+  <si>
+    <t>n_gen</t>
+  </si>
+  <si>
+    <t>popSize</t>
+  </si>
+  <si>
+    <t>p_cruza</t>
+  </si>
+  <si>
+    <t>p_mut</t>
+  </si>
+  <si>
+    <t>lambda</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Número de Generaciones</t>
+  </si>
+  <si>
+    <t>Probabilidad de Mutación</t>
+  </si>
+  <si>
+    <t>Parametro</t>
+  </si>
+  <si>
+    <t>Valores finales</t>
+  </si>
+  <si>
+    <t>Rango 
+min</t>
+  </si>
+  <si>
+    <t>Rango 
+max</t>
+  </si>
+  <si>
+    <t>Tamaño de
+ Población</t>
+  </si>
+  <si>
+    <t>Probabilidad de
+ Cruza</t>
+  </si>
+  <si>
+    <t>Factor de Penalización (λ)</t>
+  </si>
+  <si>
+    <t>Entero 
+(i)</t>
+  </si>
+  <si>
+    <t>Real 
+(r)</t>
+  </si>
+  <si>
+    <t>Tabla 4: Calibración de parametros</t>
+  </si>
+  <si>
+    <t>Función de aptitud</t>
+  </si>
+  <si>
+    <t>Tabla 3: Calibración de parametros</t>
+  </si>
+  <si>
+    <t>Binaria (Cromosomas de tamaño N)</t>
+  </si>
+  <si>
+    <t>Clasíficador</t>
+  </si>
+  <si>
+    <t>1.2.penguins_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>1.3.pimadiabetes_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>1.4.wines_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>3.1.Cebolla3D_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>3.2.Cebolla10D_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>3.3.Cebolla20D_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>4.1.CancerWisconsin_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>4.2.Ionosphere_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>5.4.indicadores2015_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>5.5.indicadores2020_res_gnlpda.csv</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Mediana</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Desv. Est.</t>
+  </si>
+  <si>
+    <t>Tiempo (D.E)</t>
+  </si>
+  <si>
+    <t>Tiempo 
+(Media)</t>
+  </si>
+  <si>
+    <t>Tabla 3: Resumen de rendimiento y tiempo de GNLPDA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -593,8 +869,68 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,8 +943,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBA58"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0D7E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEE7D1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9ECF4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3EA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -631,22 +997,137 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -655,11 +1136,98 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1219,6 +1787,1071 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4EE8590-F4BD-4325-A2C4-1CEA957237FA}">
+  <dimension ref="D3:K9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="4:11" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="5" spans="4:11" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+    </row>
+    <row r="6" spans="4:11" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+    </row>
+    <row r="7" spans="4:11" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+    </row>
+    <row r="8" spans="4:11" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+    </row>
+    <row r="9" spans="4:11" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65027B9-F002-4D22-8D70-8E6FEF0951ED}">
+  <dimension ref="C7:H16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="3:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+    </row>
+    <row r="8" spans="3:8" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="C8" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" ht="48" x14ac:dyDescent="0.25">
+      <c r="C9" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C10" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="C11" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="C12" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="C13" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C14" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C15" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="C16" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C7:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB38107B-E033-4843-852C-AAABC10D6FE4}">
+  <dimension ref="D3:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" spans="4:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="D4" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="4:9" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="D5" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" s="28">
+        <v>20</v>
+      </c>
+      <c r="H5" s="29">
+        <v>100</v>
+      </c>
+      <c r="I5" s="29">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="4:9" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="D6" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="G6" s="30">
+        <v>20</v>
+      </c>
+      <c r="H6" s="31">
+        <v>100</v>
+      </c>
+      <c r="I6" s="31">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="4:9" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="D7" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="28">
+        <v>0.4</v>
+      </c>
+      <c r="H7" s="29">
+        <v>0.95</v>
+      </c>
+      <c r="I7" s="29">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" spans="4:9" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="D8" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" s="30">
+        <v>0.05</v>
+      </c>
+      <c r="H8" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="31">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="4:9" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="D9" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="G9" s="28">
+        <v>0.01</v>
+      </c>
+      <c r="H9" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="I9" s="29">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+    </row>
+    <row r="24" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+    </row>
+    <row r="25" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+    </row>
+    <row r="26" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+    </row>
+    <row r="27" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{876F9CF3-7671-42E9-8B46-5CFD05DE74DC}">
+  <dimension ref="E10:AA37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="20:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="T10" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="U10" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="V10" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="W10" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="X10" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y10" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z10" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="AA10" s="27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="20:27" x14ac:dyDescent="0.25">
+      <c r="T11" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="U11" s="27">
+        <v>0.94</v>
+      </c>
+      <c r="V11" s="27">
+        <v>1</v>
+      </c>
+      <c r="W11" s="27">
+        <v>0.98</v>
+      </c>
+      <c r="X11" s="27">
+        <v>0.98</v>
+      </c>
+      <c r="Y11" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="Z11" s="27">
+        <v>4.68</v>
+      </c>
+      <c r="AA11" s="27">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="12" spans="20:27" x14ac:dyDescent="0.25">
+      <c r="T12" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="U12" s="27">
+        <v>0.83</v>
+      </c>
+      <c r="V12" s="27">
+        <v>1</v>
+      </c>
+      <c r="W12" s="27">
+        <v>0.94</v>
+      </c>
+      <c r="X12" s="27">
+        <v>0.94</v>
+      </c>
+      <c r="Y12" s="27">
+        <v>0.04</v>
+      </c>
+      <c r="Z12" s="27">
+        <v>882.39</v>
+      </c>
+      <c r="AA12" s="27">
+        <v>441.21</v>
+      </c>
+    </row>
+    <row r="13" spans="20:27" x14ac:dyDescent="0.25">
+      <c r="T13" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="U13" s="27">
+        <v>0.94</v>
+      </c>
+      <c r="V13" s="27">
+        <v>0.98</v>
+      </c>
+      <c r="W13" s="27">
+        <v>0.96</v>
+      </c>
+      <c r="X13" s="27">
+        <v>0.96</v>
+      </c>
+      <c r="Y13" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="Z13" s="27">
+        <v>2496.7800000000002</v>
+      </c>
+      <c r="AA13" s="27">
+        <v>958.95</v>
+      </c>
+    </row>
+    <row r="14" spans="20:27" x14ac:dyDescent="0.25">
+      <c r="T14" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="U14" s="27">
+        <v>0.84</v>
+      </c>
+      <c r="V14" s="27">
+        <v>0.95</v>
+      </c>
+      <c r="W14" s="27">
+        <v>0.89</v>
+      </c>
+      <c r="X14" s="27">
+        <v>0.89</v>
+      </c>
+      <c r="Y14" s="27">
+        <v>0.03</v>
+      </c>
+      <c r="Z14" s="27">
+        <v>3221.6</v>
+      </c>
+      <c r="AA14" s="27">
+        <v>1585.83</v>
+      </c>
+    </row>
+    <row r="15" spans="20:27" x14ac:dyDescent="0.25">
+      <c r="T15" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="U15" s="27">
+        <v>0.93</v>
+      </c>
+      <c r="V15" s="27">
+        <v>0.99</v>
+      </c>
+      <c r="W15" s="27">
+        <v>0.97</v>
+      </c>
+      <c r="X15" s="27">
+        <v>0.97</v>
+      </c>
+      <c r="Y15" s="27">
+        <v>0.02</v>
+      </c>
+      <c r="Z15" s="27">
+        <v>3.83</v>
+      </c>
+      <c r="AA15" s="27">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="20:27" x14ac:dyDescent="0.25">
+      <c r="T16" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="U16" s="27">
+        <v>0.82</v>
+      </c>
+      <c r="V16" s="27">
+        <v>0.97</v>
+      </c>
+      <c r="W16" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="X16" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="Y16" s="27">
+        <v>0.03</v>
+      </c>
+      <c r="Z16" s="27">
+        <v>2238.17</v>
+      </c>
+      <c r="AA16" s="27">
+        <v>1102.28</v>
+      </c>
+    </row>
+    <row r="17" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="T17" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="U17" s="27">
+        <v>0.71</v>
+      </c>
+      <c r="V17" s="27">
+        <v>0.93</v>
+      </c>
+      <c r="W17" s="27">
+        <v>0.83</v>
+      </c>
+      <c r="X17" s="27">
+        <v>0.82</v>
+      </c>
+      <c r="Y17" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="Z17" s="27">
+        <v>1772.73</v>
+      </c>
+      <c r="AA17" s="27">
+        <v>596.16</v>
+      </c>
+    </row>
+    <row r="18" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="T18" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="U18" s="27">
+        <v>0.72</v>
+      </c>
+      <c r="V18" s="27">
+        <v>0.81</v>
+      </c>
+      <c r="W18" s="27">
+        <v>0.77</v>
+      </c>
+      <c r="X18" s="27">
+        <v>0.77</v>
+      </c>
+      <c r="Y18" s="27">
+        <v>0.02</v>
+      </c>
+      <c r="Z18" s="27">
+        <v>515.97</v>
+      </c>
+      <c r="AA18" s="27">
+        <v>292.13</v>
+      </c>
+    </row>
+    <row r="19" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="T19" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="U19" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="V19" s="27">
+        <v>0.94</v>
+      </c>
+      <c r="W19" s="27">
+        <v>0.92</v>
+      </c>
+      <c r="X19" s="27">
+        <v>0.92</v>
+      </c>
+      <c r="Y19" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="Z19" s="27">
+        <v>1245.8399999999999</v>
+      </c>
+      <c r="AA19" s="27">
+        <v>321.24</v>
+      </c>
+    </row>
+    <row r="20" spans="5:27" x14ac:dyDescent="0.25">
+      <c r="T20" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="U20" s="27">
+        <v>0.91</v>
+      </c>
+      <c r="V20" s="27">
+        <v>0.96</v>
+      </c>
+      <c r="W20" s="27">
+        <v>0.93</v>
+      </c>
+      <c r="X20" s="27">
+        <v>0.93</v>
+      </c>
+      <c r="Y20" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="Z20" s="27">
+        <v>715.43</v>
+      </c>
+      <c r="AA20" s="27">
+        <v>39.82</v>
+      </c>
+    </row>
+    <row r="26" spans="5:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37"/>
+    </row>
+    <row r="27" spans="5:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="E27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="5:27" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="E28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="7">
+        <v>4</v>
+      </c>
+      <c r="G28" s="7">
+        <v>0.94</v>
+      </c>
+      <c r="H28" s="7">
+        <v>1</v>
+      </c>
+      <c r="I28" s="7">
+        <v>0.98</v>
+      </c>
+      <c r="J28" s="7">
+        <v>0.98</v>
+      </c>
+      <c r="K28" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="L28" s="7">
+        <v>4.68</v>
+      </c>
+      <c r="M28" s="7">
+        <v>5.68</v>
+      </c>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+    </row>
+    <row r="29" spans="5:27" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="E29" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="7">
+        <v>13</v>
+      </c>
+      <c r="G29" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="H29" s="7">
+        <v>1</v>
+      </c>
+      <c r="I29" s="7">
+        <v>0.94</v>
+      </c>
+      <c r="J29" s="7">
+        <v>0.94</v>
+      </c>
+      <c r="K29" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="L29" s="7">
+        <v>882.39</v>
+      </c>
+      <c r="M29" s="7">
+        <v>441.21</v>
+      </c>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+    </row>
+    <row r="30" spans="5:27" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="E30" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="35">
+        <v>30</v>
+      </c>
+      <c r="G30" s="35">
+        <v>0.94</v>
+      </c>
+      <c r="H30" s="35">
+        <v>0.98</v>
+      </c>
+      <c r="I30" s="35">
+        <v>0.96</v>
+      </c>
+      <c r="J30" s="35">
+        <v>0.96</v>
+      </c>
+      <c r="K30" s="35">
+        <v>0.01</v>
+      </c>
+      <c r="L30" s="35">
+        <v>2496.7800000000002</v>
+      </c>
+      <c r="M30" s="35">
+        <v>958.95</v>
+      </c>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+    </row>
+    <row r="31" spans="5:27" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="E31" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="35">
+        <v>34</v>
+      </c>
+      <c r="G31" s="35">
+        <v>0.84</v>
+      </c>
+      <c r="H31" s="35">
+        <v>0.95</v>
+      </c>
+      <c r="I31" s="35">
+        <v>0.89</v>
+      </c>
+      <c r="J31" s="35">
+        <v>0.89</v>
+      </c>
+      <c r="K31" s="35">
+        <v>0.03</v>
+      </c>
+      <c r="L31" s="35">
+        <v>3221.6</v>
+      </c>
+      <c r="M31" s="35">
+        <v>1585.83</v>
+      </c>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+    </row>
+    <row r="32" spans="5:27" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="E32" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="7">
+        <v>3</v>
+      </c>
+      <c r="G32" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="H32" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="I32" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="J32" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="K32" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="L32" s="7">
+        <v>3.83</v>
+      </c>
+      <c r="M32" s="7">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+    </row>
+    <row r="33" spans="5:16" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="E33" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="35">
+        <v>10</v>
+      </c>
+      <c r="G33" s="35">
+        <v>0.82</v>
+      </c>
+      <c r="H33" s="35">
+        <v>0.97</v>
+      </c>
+      <c r="I33" s="35">
+        <v>0.9</v>
+      </c>
+      <c r="J33" s="35">
+        <v>0.9</v>
+      </c>
+      <c r="K33" s="35">
+        <v>0.03</v>
+      </c>
+      <c r="L33" s="35">
+        <v>2238.17</v>
+      </c>
+      <c r="M33" s="35">
+        <v>1102.28</v>
+      </c>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+    </row>
+    <row r="34" spans="5:16" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="E34" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="7">
+        <v>20</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="H34" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="I34" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="J34" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="K34" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="L34" s="7">
+        <v>1772.73</v>
+      </c>
+      <c r="M34" s="7">
+        <v>596.16</v>
+      </c>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+    </row>
+    <row r="35" spans="5:16" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="E35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="7">
+        <v>8</v>
+      </c>
+      <c r="G35" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="H35" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="I35" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="J35" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="K35" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="L35" s="7">
+        <v>515.97</v>
+      </c>
+      <c r="M35" s="7">
+        <v>292.13</v>
+      </c>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+    </row>
+    <row r="36" spans="5:16" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="E36" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="7">
+        <v>12</v>
+      </c>
+      <c r="G36" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="H36" s="7">
+        <v>0.94</v>
+      </c>
+      <c r="I36" s="7">
+        <v>0.92</v>
+      </c>
+      <c r="J36" s="7">
+        <v>0.92</v>
+      </c>
+      <c r="K36" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="L36" s="7">
+        <v>1245.8399999999999</v>
+      </c>
+      <c r="M36" s="7">
+        <v>321.24</v>
+      </c>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+    </row>
+    <row r="37" spans="5:16" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="E37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="7">
+        <v>12</v>
+      </c>
+      <c r="G37" s="7">
+        <v>0.91</v>
+      </c>
+      <c r="H37" s="7">
+        <v>0.96</v>
+      </c>
+      <c r="I37" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="J37" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="K37" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="L37" s="7">
+        <v>715.43</v>
+      </c>
+      <c r="M37" s="7">
+        <v>39.82</v>
+      </c>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E26:M26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B65E1C-9B7D-42D0-B69B-48D45C721FC3}">
   <dimension ref="B4:F14"/>
@@ -2293,4 +3926,258 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3754401-6611-4767-B988-2572F166D1D1}">
+  <dimension ref="C3:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="50.5703125" customWidth="1"/>
+    <col min="4" max="4" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="C3" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
+    </row>
+    <row r="4" spans="3:5" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="C4" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C5" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C6" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C7" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C8" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C9" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C10" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="C11" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F9C3E64-A213-4737-8650-48BC4F1F536F}">
+  <dimension ref="E3:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="54" customWidth="1"/>
+    <col min="6" max="6" width="36.42578125" customWidth="1"/>
+    <col min="7" max="7" width="79" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="5:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="E3" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" s="13"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="5:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="E4" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="5:7" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="E5" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="5:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="E6" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="5:7" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="E7" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="5:7" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="E8" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="5:7" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="E9" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="5:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="E10" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="5:7" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="E11" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="5:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="E12" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>